--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MAINE_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MAINE_2019.xlsx
@@ -535,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="D10">
-        <v>0.09677419354838709</v>
+        <v>0.09677419354838708</v>
       </c>
     </row>
     <row r="11">
